--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N76_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N76_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>63.69370483412185</v>
+        <v>10.3502270355448</v>
       </c>
       <c r="D2" t="n">
-        <v>32.23554396166804</v>
+        <v>5.238275893771057</v>
       </c>
       <c r="E2" t="n">
-        <v>10.86064511845628</v>
+        <v>1.764854831749146</v>
       </c>
       <c r="F2" t="n">
-        <v>19.44166589452486</v>
+        <v>3.159270707860289</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>51.7499176362394</v>
+        <v>8.409361615888901</v>
       </c>
       <c r="D3" t="n">
-        <v>35.35533905932738</v>
+        <v>5.745242597140699</v>
       </c>
       <c r="E3" t="n">
-        <v>10.86064511845628</v>
+        <v>1.764854831749146</v>
       </c>
       <c r="F3" t="n">
-        <v>19.44166589452486</v>
+        <v>3.159270707860289</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>40.10762745519339</v>
+        <v>6.517489461468926</v>
       </c>
       <c r="D4" t="n">
-        <v>73.11326893520676</v>
+        <v>11.8809062019711</v>
       </c>
       <c r="E4" t="n">
-        <v>10.86064511845628</v>
+        <v>1.764854831749146</v>
       </c>
       <c r="F4" t="n">
-        <v>19.44166589452486</v>
+        <v>3.159270707860289</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>43.30415684434925</v>
+        <v>7.036925487206753</v>
       </c>
       <c r="D5" t="n">
-        <v>80.00723251857465</v>
+        <v>13.00117528426838</v>
       </c>
       <c r="E5" t="n">
-        <v>10.86064511845628</v>
+        <v>1.764854831749146</v>
       </c>
       <c r="F5" t="n">
-        <v>19.44166589452486</v>
+        <v>3.159270707860289</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>68.08953269721216</v>
+        <v>11.06454906329698</v>
       </c>
       <c r="D6" t="n">
-        <v>67.26731030990196</v>
+        <v>10.93093792535907</v>
       </c>
       <c r="E6" t="n">
-        <v>10.86064511845628</v>
+        <v>1.764854831749146</v>
       </c>
       <c r="F6" t="n">
-        <v>19.44166589452486</v>
+        <v>3.159270707860289</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>64.59489143887464</v>
+        <v>10.49666985881713</v>
       </c>
       <c r="D7" t="n">
-        <v>76.36232477312538</v>
+        <v>12.40887777563287</v>
       </c>
       <c r="E7" t="n">
-        <v>10.86064511845628</v>
+        <v>1.764854831749146</v>
       </c>
       <c r="F7" t="n">
-        <v>19.44166589452486</v>
+        <v>3.159270707860289</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
